--- a/public/templates/products-import-template.xlsx
+++ b/public/templates/products-import-template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:I2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,25 +426,7 @@
         <v>is_active</v>
       </c>
       <c r="I1" t="str">
-        <v>vendor_id</v>
-      </c>
-      <c r="J1" t="str">
-        <v>image_1</v>
-      </c>
-      <c r="K1" t="str">
-        <v>image_2</v>
-      </c>
-      <c r="L1" t="str">
-        <v>image_3</v>
-      </c>
-      <c r="M1" t="str">
-        <v>image_4</v>
-      </c>
-      <c r="N1" t="str">
-        <v>image_5</v>
-      </c>
-      <c r="O1" t="str">
-        <v>video_url</v>
+        <v>image_url</v>
       </c>
     </row>
     <row r="2">
@@ -473,37 +455,19 @@
         <v>TRUE</v>
       </c>
       <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
         <v>https://drive.google.com/file/d/EXAMPLE_FILE_ID/view</v>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v>https://www.youtube.com/watch?v=EXAMPLE</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -633,147 +597,63 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>vendor_id</v>
+        <v>image_url</v>
       </c>
       <c r="B10" t="str">
         <v>no</v>
       </c>
       <c r="C10" t="str">
-        <v>uuid</v>
+        <v>url</v>
       </c>
       <c r="D10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>image_1</v>
-      </c>
-      <c r="B11" t="str">
-        <v>no</v>
-      </c>
-      <c r="C11" t="str">
-        <v>url</v>
-      </c>
-      <c r="D11" t="str">
         <v>Drive share URL or any https URL — re-hosted on import</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>image_2</v>
+        <v>Drive sharing required</v>
       </c>
       <c r="B12" t="str">
-        <v>no</v>
+        <v/>
       </c>
       <c r="C12" t="str">
-        <v>url</v>
+        <v/>
       </c>
       <c r="D12" t="str">
-        <v>Drive share URL or any https URL — re-hosted on import</v>
+        <v>Right-click folder → Share → "Anyone with the link"</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>image_3</v>
+        <v>Image size cap</v>
       </c>
       <c r="B13" t="str">
-        <v>no</v>
+        <v/>
       </c>
       <c r="C13" t="str">
-        <v>url</v>
+        <v/>
       </c>
       <c r="D13" t="str">
-        <v>Drive share URL or any https URL — re-hosted on import</v>
+        <v>Keep files under 25 MB to avoid Drive virus-scan interstitial</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>image_4</v>
+        <v>Boolean values</v>
       </c>
       <c r="B14" t="str">
-        <v>no</v>
+        <v/>
       </c>
       <c r="C14" t="str">
-        <v>url</v>
+        <v/>
       </c>
       <c r="D14" t="str">
-        <v>Drive share URL or any https URL — re-hosted on import</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>image_5</v>
-      </c>
-      <c r="B15" t="str">
-        <v>no</v>
-      </c>
-      <c r="C15" t="str">
-        <v>url</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Drive share URL or any https URL — re-hosted on import</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>video_url</v>
-      </c>
-      <c r="B16" t="str">
-        <v>no</v>
-      </c>
-      <c r="C16" t="str">
-        <v>url</v>
-      </c>
-      <c r="D16" t="str">
-        <v>YouTube/Vimeo/Drive — stored as-is</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Drive sharing required</v>
-      </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <v>Right-click folder → Share → "Anyone with the link"</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Image size cap</v>
-      </c>
-      <c r="B19" t="str">
-        <v/>
-      </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19" t="str">
-        <v>Keep files under 25 MB to avoid Drive virus-scan interstitial</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Boolean values</v>
-      </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
         <v>TRUE / FALSE / yes / no / 1 / 0 all accepted</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/products-import-template.xlsx
+++ b/public/templates/products-import-template.xlsx
@@ -398,23 +398,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:AC2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>sku</v>
+        <v>name</v>
       </c>
       <c r="B1" t="str">
-        <v>name</v>
+        <v>category</v>
       </c>
       <c r="C1" t="str">
-        <v>description</v>
+        <v>brand</v>
       </c>
       <c r="D1" t="str">
-        <v>brand</v>
+        <v>model</v>
       </c>
       <c r="E1" t="str">
-        <v>model</v>
+        <v>screen_size</v>
       </c>
       <c r="F1" t="str">
         <v>year_from</v>
@@ -423,27 +423,87 @@
         <v>year_to</v>
       </c>
       <c r="H1" t="str">
-        <v>is_active</v>
+        <v>description</v>
       </c>
       <c r="I1" t="str">
-        <v>image_url</v>
+        <v>active</v>
+      </c>
+      <c r="J1" t="str">
+        <v>component_sku_1</v>
+      </c>
+      <c r="K1" t="str">
+        <v>component_sku_2</v>
+      </c>
+      <c r="L1" t="str">
+        <v>component_sku_3</v>
+      </c>
+      <c r="M1" t="str">
+        <v>component_sku_4</v>
+      </c>
+      <c r="N1" t="str">
+        <v>component_sku_5</v>
+      </c>
+      <c r="O1" t="str">
+        <v>media_1</v>
+      </c>
+      <c r="P1" t="str">
+        <v>media_2</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>media_3</v>
+      </c>
+      <c r="R1" t="str">
+        <v>media_4</v>
+      </c>
+      <c r="S1" t="str">
+        <v>media_5</v>
+      </c>
+      <c r="T1" t="str">
+        <v>media_6</v>
+      </c>
+      <c r="U1" t="str">
+        <v>media_7</v>
+      </c>
+      <c r="V1" t="str">
+        <v>media_8</v>
+      </c>
+      <c r="W1" t="str">
+        <v>media_9</v>
+      </c>
+      <c r="X1" t="str">
+        <v>media_10</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>media_11</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>media_12</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>media_13</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>media_14</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>media_15</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>PRD-001</v>
+        <v>Audi A4 9 Inch Android Head Unit Kit</v>
       </c>
       <c r="B2" t="str">
-        <v>Android Head Unit 10"</v>
+        <v>Android Head Units</v>
       </c>
       <c r="C2" t="str">
-        <v>10-inch Android car head unit with GPS and Bluetooth</v>
+        <v>Audi</v>
       </c>
       <c r="D2" t="str">
-        <v>Honda</v>
+        <v>A4</v>
       </c>
       <c r="E2" t="str">
-        <v>Civic</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>2018</v>
@@ -452,22 +512,82 @@
         <v>2022</v>
       </c>
       <c r="H2" t="str">
+        <v>9-inch Android head unit kit for Audi A4 2018-2022. Includes casing, dash kit, and cable harness.</v>
+      </c>
+      <c r="I2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="I2" t="str">
-        <v>https://drive.google.com/file/d/EXAMPLE_FILE_ID/view</v>
+      <c r="J2" t="str">
+        <v>CASING-A4-9IN-001</v>
+      </c>
+      <c r="K2" t="str">
+        <v>DASH-AUDI-A4-001</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v>https://drive.google.com/file/d/EXAMPLE_PRIMARY_IMAGE_ID/view</v>
+      </c>
+      <c r="P2" t="str">
+        <v>https://drive.google.com/file/d/EXAMPLE_GALLERY_IMAGE_ID/view</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>https://www.youtube.com/watch?v=EXAMPLE_VIDEO_ID</v>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v/>
+      </c>
+      <c r="AB2" t="str">
+        <v/>
+      </c>
+      <c r="AC2" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,7 +605,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>sku</v>
+        <v>name</v>
       </c>
       <c r="B2" t="str">
         <v>YES</v>
@@ -494,26 +614,26 @@
         <v>text</v>
       </c>
       <c r="D2" t="str">
-        <v>pattern: /^[A-Z0-9-]{3,40}$/i</v>
+        <v>Required. Product display name shown to customers.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>name</v>
+        <v>category</v>
       </c>
       <c r="B3" t="str">
-        <v>YES</v>
+        <v>no</v>
       </c>
       <c r="C3" t="str">
         <v>text</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>Optional. Existing category name (case-insensitive match). Leave blank for uncategorised.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>description</v>
+        <v>brand</v>
       </c>
       <c r="B4" t="str">
         <v>no</v>
@@ -522,12 +642,12 @@
         <v>text</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>Optional. Vehicle brand, e.g. "Audi", "Honda".</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>brand</v>
+        <v>model</v>
       </c>
       <c r="B5" t="str">
         <v>no</v>
@@ -536,12 +656,12 @@
         <v>text</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>Optional. Vehicle model, e.g. "A4", "Civic".</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>model</v>
+        <v>screen_size</v>
       </c>
       <c r="B6" t="str">
         <v>no</v>
@@ -550,7 +670,7 @@
         <v>text</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>Optional. One of: 6, 7, 8, 9, 10, 12.5</v>
       </c>
     </row>
     <row r="7">
@@ -564,7 +684,7 @@
         <v>integer</v>
       </c>
       <c r="D7" t="str">
-        <v>min: 1900</v>
+        <v>Optional. Earliest model year, e.g. 2018.</v>
       </c>
     </row>
     <row r="8">
@@ -578,82 +698,376 @@
         <v>integer</v>
       </c>
       <c r="D8" t="str">
-        <v>min: 1900</v>
+        <v>Optional. Latest model year, e.g. 2022.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>is_active</v>
+        <v>description</v>
       </c>
       <c r="B9" t="str">
         <v>no</v>
       </c>
       <c r="C9" t="str">
-        <v>boolean</v>
+        <v>text</v>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>Optional free-text description shown on the product/component page.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>image_url</v>
+        <v>active</v>
       </c>
       <c r="B10" t="str">
         <v>no</v>
       </c>
       <c r="C10" t="str">
-        <v>url</v>
+        <v>boolean</v>
       </c>
       <c r="D10" t="str">
-        <v>Drive share URL or any https URL — re-hosted on import</v>
+        <v>Optional. TRUE/FALSE. Defaults to TRUE. Inactive products are hidden from the catalog.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>component_sku_1</v>
+      </c>
+      <c r="B11" t="str">
+        <v>YES</v>
+      </c>
+      <c r="C11" t="str">
+        <v>text</v>
+      </c>
+      <c r="D11" t="str">
+        <v>REQUIRED. SKU of an existing component from the component library. At least 1 component per product.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Drive sharing required</v>
+        <v>component_sku_2</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>no</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>text</v>
       </c>
       <c r="D12" t="str">
-        <v>Right-click folder → Share → "Anyone with the link"</v>
+        <v>Optional. Additional component SKU (must exist in component library).</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Image size cap</v>
+        <v>component_sku_3</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>no</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>text</v>
       </c>
       <c r="D13" t="str">
-        <v>Keep files under 25 MB to avoid Drive virus-scan interstitial</v>
+        <v>Optional. Additional component SKU.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>component_sku_4</v>
+      </c>
+      <c r="B14" t="str">
+        <v>no</v>
+      </c>
+      <c r="C14" t="str">
+        <v>text</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Optional. Additional component SKU.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>component_sku_5</v>
+      </c>
+      <c r="B15" t="str">
+        <v>no</v>
+      </c>
+      <c r="C15" t="str">
+        <v>text</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Optional. Additional component SKU.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>media_1</v>
+      </c>
+      <c r="B16" t="str">
+        <v>no</v>
+      </c>
+      <c r="C16" t="str">
+        <v>url</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Optional but recommended. PRIMARY image/video. Drive image link, direct image URL, YouTube/Vimeo, or Drive video link.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>media_2</v>
+      </c>
+      <c r="B17" t="str">
+        <v>no</v>
+      </c>
+      <c r="C17" t="str">
+        <v>url</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Optional. Gallery slot. Drive/Dropbox/CDN image, YouTube/Vimeo, or direct video URL.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>media_3</v>
+      </c>
+      <c r="B18" t="str">
+        <v>no</v>
+      </c>
+      <c r="C18" t="str">
+        <v>url</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Optional. Gallery slot. Drive/Dropbox/CDN image, YouTube/Vimeo, or direct video URL.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>media_4</v>
+      </c>
+      <c r="B19" t="str">
+        <v>no</v>
+      </c>
+      <c r="C19" t="str">
+        <v>url</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Optional. Gallery slot. Drive/Dropbox/CDN image, YouTube/Vimeo, or direct video URL.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>media_5</v>
+      </c>
+      <c r="B20" t="str">
+        <v>no</v>
+      </c>
+      <c r="C20" t="str">
+        <v>url</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Optional. Gallery slot. Drive/Dropbox/CDN image, YouTube/Vimeo, or direct video URL.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>media_6</v>
+      </c>
+      <c r="B21" t="str">
+        <v>no</v>
+      </c>
+      <c r="C21" t="str">
+        <v>url</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Optional. Gallery slot. Drive/Dropbox/CDN image, YouTube/Vimeo, or direct video URL.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>media_7</v>
+      </c>
+      <c r="B22" t="str">
+        <v>no</v>
+      </c>
+      <c r="C22" t="str">
+        <v>url</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Optional. Gallery slot. Drive/Dropbox/CDN image, YouTube/Vimeo, or direct video URL.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>media_8</v>
+      </c>
+      <c r="B23" t="str">
+        <v>no</v>
+      </c>
+      <c r="C23" t="str">
+        <v>url</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Optional. Gallery slot. Drive/Dropbox/CDN image, YouTube/Vimeo, or direct video URL.</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>media_9</v>
+      </c>
+      <c r="B24" t="str">
+        <v>no</v>
+      </c>
+      <c r="C24" t="str">
+        <v>url</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Optional. Gallery slot. Drive/Dropbox/CDN image, YouTube/Vimeo, or direct video URL.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>media_10</v>
+      </c>
+      <c r="B25" t="str">
+        <v>no</v>
+      </c>
+      <c r="C25" t="str">
+        <v>url</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Optional. Gallery slot. Drive/Dropbox/CDN image, YouTube/Vimeo, or direct video URL.</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>media_11</v>
+      </c>
+      <c r="B26" t="str">
+        <v>no</v>
+      </c>
+      <c r="C26" t="str">
+        <v>url</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Optional. Gallery slot. Drive/Dropbox/CDN image, YouTube/Vimeo, or direct video URL.</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>media_12</v>
+      </c>
+      <c r="B27" t="str">
+        <v>no</v>
+      </c>
+      <c r="C27" t="str">
+        <v>url</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Optional. Gallery slot. Drive/Dropbox/CDN image, YouTube/Vimeo, or direct video URL.</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>media_13</v>
+      </c>
+      <c r="B28" t="str">
+        <v>no</v>
+      </c>
+      <c r="C28" t="str">
+        <v>url</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Optional. Gallery slot. Drive/Dropbox/CDN image, YouTube/Vimeo, or direct video URL.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>media_14</v>
+      </c>
+      <c r="B29" t="str">
+        <v>no</v>
+      </c>
+      <c r="C29" t="str">
+        <v>url</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Optional. Gallery slot. Drive/Dropbox/CDN image, YouTube/Vimeo, or direct video URL.</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>media_15</v>
+      </c>
+      <c r="B30" t="str">
+        <v>no</v>
+      </c>
+      <c r="C30" t="str">
+        <v>url</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Optional. Gallery slot. Drive/Dropbox/CDN image, YouTube/Vimeo, or direct video URL.</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Drive sharing</v>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v>Right-click folder → Share → "Anyone with the link → Viewer"</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Media size cap</v>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v>Images: under 25 MB to avoid Drive virus-scan interstitial. Videos: up to 2 GB.</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
         <v>Boolean values</v>
       </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
         <v>TRUE / FALSE / yes / no / 1 / 0 all accepted</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>YouTube/Vimeo</v>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v>Stored as-is and embedded. No download required.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D35"/>
   </ignoredErrors>
 </worksheet>
 </file>